--- a/BVSimulationFiles/700.xlsx
+++ b/BVSimulationFiles/700.xlsx
@@ -1,34 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\BVSimulationFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D4BD99-40C9-4AA9-85C2-1C53BD5F0E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +51,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,240 +353,395 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="n">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="B1">
         <v>0</v>
       </c>
-      <c r="C1" t="n">
-        <v>0.955</v>
+      <c r="C1">
+        <v>0.10526315789473679</v>
+      </c>
+      <c r="D1">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="E1">
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="F1">
+        <v>0.42105263157894729</v>
+      </c>
+      <c r="G1">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="H1">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="I1">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="J1">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="K1">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="L1">
+        <v>1.0526315789473679</v>
+      </c>
+      <c r="M1">
+        <v>1.1578947368421051</v>
+      </c>
+      <c r="N1">
+        <v>1.263157894736842</v>
+      </c>
+      <c r="O1">
+        <v>1.368421052631579</v>
+      </c>
+      <c r="P1">
+        <v>1.4736842105263159</v>
+      </c>
+      <c r="Q1">
+        <v>1.5789473684210531</v>
+      </c>
+      <c r="R1">
+        <v>1.6842105263157889</v>
+      </c>
+      <c r="S1">
+        <v>1.7894736842105261</v>
+      </c>
+      <c r="T1">
+        <v>1.8947368421052631</v>
+      </c>
+      <c r="U1">
+        <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0001</v>
+      <c r="B2">
+        <v>6.3661977236758142E-3</v>
+      </c>
+      <c r="C2">
+        <v>5.9182424809030741E-3</v>
+      </c>
+      <c r="D2">
+        <v>5.5018074497601597E-3</v>
+      </c>
+      <c r="E2">
+        <v>5.1146747217456811E-3</v>
+      </c>
+      <c r="F2">
+        <v>4.7547824507025681E-3</v>
+      </c>
+      <c r="G2">
+        <v>4.4202138715466214E-3</v>
+      </c>
+      <c r="H2">
+        <v>4.1091870916883256E-3</v>
+      </c>
+      <c r="I2">
+        <v>3.8200456007776362E-3</v>
+      </c>
+      <c r="J2">
+        <v>3.5512494482272182E-3</v>
+      </c>
+      <c r="K2">
+        <v>3.301367041526118E-3</v>
+      </c>
+      <c r="L2">
+        <v>3.0690675216621839E-3</v>
+      </c>
+      <c r="M2">
+        <v>2.8531136750451929E-3</v>
+      </c>
+      <c r="N2">
+        <v>2.6523553441799778E-3</v>
+      </c>
+      <c r="O2">
+        <v>2.465723301995197E-3</v>
+      </c>
+      <c r="P2">
+        <v>2.2922235572028051E-3</v>
+      </c>
+      <c r="Q2">
+        <v>2.130932060358861E-3</v>
+      </c>
+      <c r="R2">
+        <v>1.9809897824305052E-3</v>
+      </c>
+      <c r="S2">
+        <v>1.841598139657808E-3</v>
+      </c>
+      <c r="T2">
+        <v>1.7120147403436069E-3</v>
+      </c>
+      <c r="U2">
+        <v>1.591549430918954E-3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.003684210526315789</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0001</v>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>0.23874999999999999</v>
+      </c>
+      <c r="B3">
+        <v>7.9577471545947669E-3</v>
+      </c>
+      <c r="C3">
+        <v>7.3978031011288428E-3</v>
+      </c>
+      <c r="D3">
+        <v>6.8772593122001999E-3</v>
+      </c>
+      <c r="E3">
+        <v>6.393343402182102E-3</v>
+      </c>
+      <c r="F3">
+        <v>5.9434780633782092E-3</v>
+      </c>
+      <c r="G3">
+        <v>5.5252673394332753E-3</v>
+      </c>
+      <c r="H3">
+        <v>5.1364838646104074E-3</v>
+      </c>
+      <c r="I3">
+        <v>4.7750570009720446E-3</v>
+      </c>
+      <c r="J3">
+        <v>4.4390618102840233E-3</v>
+      </c>
+      <c r="K3">
+        <v>4.1267088019076468E-3</v>
+      </c>
+      <c r="L3">
+        <v>3.8363344020777312E-3</v>
+      </c>
+      <c r="M3">
+        <v>3.5663920938064919E-3</v>
+      </c>
+      <c r="N3">
+        <v>3.315444180224972E-3</v>
+      </c>
+      <c r="O3">
+        <v>3.0821541274939968E-3</v>
+      </c>
+      <c r="P3">
+        <v>2.865279446503507E-3</v>
+      </c>
+      <c r="Q3">
+        <v>2.663665075448577E-3</v>
+      </c>
+      <c r="R3">
+        <v>2.476237228038131E-3</v>
+      </c>
+      <c r="S3">
+        <v>2.3019976745722601E-3</v>
+      </c>
+      <c r="T3">
+        <v>2.1400184254295089E-3</v>
+      </c>
+      <c r="U3">
+        <v>1.9894367886486922E-3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.007368421052631579</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0001</v>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>0.47749999999999998</v>
+      </c>
+      <c r="B4">
+        <v>1.1140846016432679E-2</v>
+      </c>
+      <c r="C4">
+        <v>1.035692434158038E-2</v>
+      </c>
+      <c r="D4">
+        <v>9.6281630370802802E-3</v>
+      </c>
+      <c r="E4">
+        <v>8.9506807630549429E-3</v>
+      </c>
+      <c r="F4">
+        <v>8.3208692887294933E-3</v>
+      </c>
+      <c r="G4">
+        <v>7.7353742752065864E-3</v>
+      </c>
+      <c r="H4">
+        <v>7.1910774104545694E-3</v>
+      </c>
+      <c r="I4">
+        <v>6.6850798013608622E-3</v>
+      </c>
+      <c r="J4">
+        <v>6.2146865343976317E-3</v>
+      </c>
+      <c r="K4">
+        <v>5.7773923226707054E-3</v>
+      </c>
+      <c r="L4">
+        <v>5.3708681629088227E-3</v>
+      </c>
+      <c r="M4">
+        <v>4.992948931329089E-3</v>
+      </c>
+      <c r="N4">
+        <v>4.641621852314962E-3</v>
+      </c>
+      <c r="O4">
+        <v>4.3150157784915951E-3</v>
+      </c>
+      <c r="P4">
+        <v>4.0113912251049091E-3</v>
+      </c>
+      <c r="Q4">
+        <v>3.7291311056280069E-3</v>
+      </c>
+      <c r="R4">
+        <v>3.4667321192533829E-3</v>
+      </c>
+      <c r="S4">
+        <v>3.222796744401164E-3</v>
+      </c>
+      <c r="T4">
+        <v>2.9960257956013121E-3</v>
+      </c>
+      <c r="U4">
+        <v>2.7852115041081689E-3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.01105263157894737</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0001</v>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>0.71624999999999994</v>
+      </c>
+      <c r="B5">
+        <v>-1.591549430918954E-3</v>
+      </c>
+      <c r="C5">
+        <v>-1.479560620225769E-3</v>
+      </c>
+      <c r="D5">
+        <v>-1.3754518624400399E-3</v>
+      </c>
+      <c r="E5">
+        <v>-1.27866868043642E-3</v>
+      </c>
+      <c r="F5">
+        <v>-1.188695612675642E-3</v>
+      </c>
+      <c r="G5">
+        <v>-1.1050534678866549E-3</v>
+      </c>
+      <c r="H5">
+        <v>-1.027296772922081E-3</v>
+      </c>
+      <c r="I5">
+        <v>-9.5501140019440905E-4</v>
+      </c>
+      <c r="J5">
+        <v>-8.8781236205680454E-4</v>
+      </c>
+      <c r="K5">
+        <v>-8.2534176038152939E-4</v>
+      </c>
+      <c r="L5">
+        <v>-7.6726688041554609E-4</v>
+      </c>
+      <c r="M5">
+        <v>-7.1327841876129834E-4</v>
+      </c>
+      <c r="N5">
+        <v>-6.6308883604499446E-4</v>
+      </c>
+      <c r="O5">
+        <v>-6.1643082549879937E-4</v>
+      </c>
+      <c r="P5">
+        <v>-5.7305588930070127E-4</v>
+      </c>
+      <c r="Q5">
+        <v>-5.3273301508971536E-4</v>
+      </c>
+      <c r="R5">
+        <v>-4.9524744560762619E-4</v>
+      </c>
+      <c r="S5">
+        <v>-4.6039953491445199E-4</v>
+      </c>
+      <c r="T5">
+        <v>-4.2800368508590168E-4</v>
+      </c>
+      <c r="U5">
+        <v>-3.9788735772973839E-4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.01473684210526316</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.01842105263157895</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.02210526315789474</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.02578947368421053</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.02947368421052632</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.0331578947368421</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0.03684210526315789</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.04052631578947368</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.04421052631578947</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0.04789473684210525</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0.05157894736842105</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>0.05526315789473684</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>0.05894736842105263</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.06263157894736841</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.0663157894736842</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0001</v>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="B6">
+        <v>3.1830988618379071E-3</v>
+      </c>
+      <c r="C6">
+        <v>2.959121240451537E-3</v>
+      </c>
+      <c r="D6">
+        <v>2.7509037248800799E-3</v>
+      </c>
+      <c r="E6">
+        <v>2.557337360872841E-3</v>
+      </c>
+      <c r="F6">
+        <v>2.377391225351284E-3</v>
+      </c>
+      <c r="G6">
+        <v>2.2101069357733098E-3</v>
+      </c>
+      <c r="H6">
+        <v>2.0545935458441628E-3</v>
+      </c>
+      <c r="I6">
+        <v>1.9100228003888181E-3</v>
+      </c>
+      <c r="J6">
+        <v>1.7756247241136091E-3</v>
+      </c>
+      <c r="K6">
+        <v>1.650683520763059E-3</v>
+      </c>
+      <c r="L6">
+        <v>1.534533760831092E-3</v>
+      </c>
+      <c r="M6">
+        <v>1.4265568375225969E-3</v>
+      </c>
+      <c r="N6">
+        <v>1.3261776720899889E-3</v>
+      </c>
+      <c r="O6">
+        <v>1.232861650997599E-3</v>
+      </c>
+      <c r="P6">
+        <v>1.146111778601403E-3</v>
+      </c>
+      <c r="Q6">
+        <v>1.0654660301794309E-3</v>
+      </c>
+      <c r="R6">
+        <v>9.9049489121525239E-4</v>
+      </c>
+      <c r="S6">
+        <v>9.2079906982890408E-4</v>
+      </c>
+      <c r="T6">
+        <v>8.5600737017180336E-4</v>
+      </c>
+      <c r="U6">
+        <v>7.9577471545947678E-4</v>
       </c>
     </row>
   </sheetData>
